--- a/web/public/forms/orig/o-hwangyeong-lh.xlsx
+++ b/web/public/forms/orig/o-hwangyeong-lh.xlsx
@@ -12008,7 +12008,7 @@
     <row r="510" ht="24" customHeight="1">
       <c r="A510" s="117" t="inlineStr">
         <is>
-          <t xml:space="preserve">      나) 세종시청</t>
+          <t xml:space="preserve">      나) 관할 시·군청</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
     <row r="545" ht="24" customHeight="1">
       <c r="A545" s="117" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2) 세종시청</t>
+          <t xml:space="preserve">      2) 관할 시·군청</t>
         </is>
       </c>
     </row>

--- a/web/public/forms/orig/o-hwangyeong-lh.xlsx
+++ b/web/public/forms/orig/o-hwangyeong-lh.xlsx
@@ -846,7 +846,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="67" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="67" t="inlineStr">
@@ -7227,7 +7227,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="67" t="inlineStr">
@@ -10895,7 +10895,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="67" t="inlineStr">
@@ -11675,7 +11675,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="67" t="inlineStr">

--- a/web/public/forms/orig/o-hwangyeong-lh.xlsx
+++ b/web/public/forms/orig/o-hwangyeong-lh.xlsx
@@ -828,7 +828,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6009,7 +6009,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
